--- a/assets/Sample questions sheet.xlsx
+++ b/assets/Sample questions sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gourab\College\My works\flutter\test_nest\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{62260EBB-E29B-47E9-8D34-C1BBF40A88C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067CBA29-1B5C-4CD8-9178-C4DCB57D8A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D157F190-8D19-4A65-AE76-A2155A2BE232}"/>
   </bookViews>
@@ -111,7 +111,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -121,26 +121,17 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color theme="0"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color theme="0"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color theme="0"/>
+        <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -149,7 +140,6 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -165,6 +155,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,60 +490,60 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74B16243-F671-4968-A132-5F29843DAEAD}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="G1:L3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.33203125" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="28.33203125" style="6" customWidth="1"/>
+    <col min="8" max="11" width="8.88671875" style="6"/>
+    <col min="12" max="12" width="16" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="7:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="G1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="7:12" x14ac:dyDescent="0.3">
+      <c r="G2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5" t="s">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="6" t="s">
+    <row r="3" spans="7:12" x14ac:dyDescent="0.3">
+      <c r="G3" s="2"/>
+      <c r="H3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="K3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="5"/>
+      <c r="L3" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="G1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/assets/Sample questions sheet.xlsx
+++ b/assets/Sample questions sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gourab\College\My works\flutter\test_nest\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067CBA29-1B5C-4CD8-9178-C4DCB57D8A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E04108-364A-4FA6-8CC2-B6DF4BE7A11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D157F190-8D19-4A65-AE76-A2155A2BE232}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>APP NMAE</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>Right option (A,B,C,D)</t>
+  </si>
+  <si>
+    <t>what is 2 + 2 ?</t>
   </si>
 </sst>
 </file>
@@ -140,9 +143,10 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -152,10 +156,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -490,53 +493,73 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74B16243-F671-4968-A132-5F29843DAEAD}">
-  <dimension ref="G1:L3"/>
+  <dimension ref="G1:L4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="7" max="7" width="28.33203125" style="6" customWidth="1"/>
-    <col min="8" max="11" width="8.88671875" style="6"/>
-    <col min="12" max="12" width="16" style="6" customWidth="1"/>
+    <col min="7" max="7" width="28.33203125" style="2" customWidth="1"/>
+    <col min="8" max="11" width="8.88671875" style="2"/>
+    <col min="12" max="12" width="16" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="7:12" ht="18" x14ac:dyDescent="0.3">
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
     </row>
     <row r="2" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="4" t="s">
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G3" s="2"/>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="3"/>
+      <c r="H3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="4"/>
+      <c r="L3" s="5"/>
+    </row>
+    <row r="4" spans="7:12" x14ac:dyDescent="0.3">
+      <c r="G4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>2</v>
+      </c>
+      <c r="J4" s="2">
+        <v>3</v>
+      </c>
+      <c r="K4" s="2">
+        <v>4</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/assets/Sample questions sheet.xlsx
+++ b/assets/Sample questions sheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gourab\College\My works\flutter\test_nest\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gourab\College\My works\flutter\test_nest_1\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E04108-364A-4FA6-8CC2-B6DF4BE7A11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE688C5-858A-4007-B47C-F53948B97E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D157F190-8D19-4A65-AE76-A2155A2BE232}"/>
+    <workbookView xWindow="5328" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{D157F190-8D19-4A65-AE76-A2155A2BE232}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>APP NMAE</t>
   </si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>Right option (A,B,C,D)</t>
-  </si>
-  <si>
-    <t>what is 2 + 2 ?</t>
   </si>
 </sst>
 </file>
@@ -493,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74B16243-F671-4968-A132-5F29843DAEAD}">
-  <dimension ref="G1:L4"/>
+  <dimension ref="G1:L3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="28.33203125" style="2" customWidth="1"/>
@@ -540,26 +537,6 @@
         <v>5</v>
       </c>
       <c r="L3" s="5"/>
-    </row>
-    <row r="4" spans="7:12" x14ac:dyDescent="0.3">
-      <c r="G4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1</v>
-      </c>
-      <c r="I4" s="2">
-        <v>2</v>
-      </c>
-      <c r="J4" s="2">
-        <v>3</v>
-      </c>
-      <c r="K4" s="2">
-        <v>4</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
